--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117450484</v>
+        <v>117450145</v>
       </c>
       <c r="B9" t="n">
-        <v>56499</v>
+        <v>97753</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,39 +1434,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516426</v>
+        <v>516424</v>
       </c>
       <c r="R9" t="n">
-        <v>6692011</v>
+        <v>6692053</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1525,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117449493</v>
+        <v>117450251</v>
       </c>
       <c r="B10" t="n">
-        <v>78514</v>
+        <v>97753</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1532,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,13 +1560,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>516504</v>
+        <v>516446</v>
       </c>
       <c r="R10" t="n">
-        <v>6692268</v>
+        <v>6692053</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1601,6 +1596,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-06-01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117450251</v>
+        <v>117449493</v>
       </c>
       <c r="B11" t="n">
-        <v>97753</v>
+        <v>78514</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516446</v>
+        <v>516504</v>
       </c>
       <c r="R11" t="n">
-        <v>6692053</v>
+        <v>6692268</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1703,11 +1703,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,10 +1836,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117450145</v>
+        <v>117450484</v>
       </c>
       <c r="B13" t="n">
-        <v>97753</v>
+        <v>56499</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1857,34 +1852,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516424</v>
+        <v>516426</v>
       </c>
       <c r="R13" t="n">
-        <v>6692053</v>
+        <v>6692011</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117449615</v>
+        <v>117450145</v>
       </c>
       <c r="B7" t="n">
-        <v>78514</v>
+        <v>97755</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,25 +1221,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>516508</v>
+        <v>516424</v>
       </c>
       <c r="R7" t="n">
-        <v>6692257</v>
+        <v>6692053</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1314,7 +1314,7 @@
         <v>117449895</v>
       </c>
       <c r="B8" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117450145</v>
+        <v>117449868</v>
       </c>
       <c r="B9" t="n">
-        <v>97753</v>
+        <v>56500</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1434,34 +1434,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>516424</v>
+        <v>516493</v>
       </c>
       <c r="R9" t="n">
-        <v>6692053</v>
+        <v>6692105</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1523,7 +1528,7 @@
         <v>117450251</v>
       </c>
       <c r="B10" t="n">
-        <v>97753</v>
+        <v>97755</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,10 +1632,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117449493</v>
+        <v>117450484</v>
       </c>
       <c r="B11" t="n">
-        <v>78514</v>
+        <v>56500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,41 +1644,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>516504</v>
+        <v>516426</v>
       </c>
       <c r="R11" t="n">
-        <v>6692268</v>
+        <v>6692011</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1729,10 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117449868</v>
+        <v>117449615</v>
       </c>
       <c r="B12" t="n">
-        <v>56499</v>
+        <v>78516</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,43 +1751,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>516493</v>
+        <v>516508</v>
       </c>
       <c r="R12" t="n">
-        <v>6692105</v>
+        <v>6692257</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1836,10 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117450484</v>
+        <v>117449493</v>
       </c>
       <c r="B13" t="n">
-        <v>56499</v>
+        <v>78516</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,46 +1853,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ramptjärnen (Ramptjärnen), Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>516426</v>
+        <v>516504</v>
       </c>
       <c r="R13" t="n">
-        <v>6692011</v>
+        <v>6692268</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,6 +1941,219 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>125408915</v>
+      </c>
+      <c r="B14" t="n">
+        <v>56843</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramptjärnen, Ramptjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>516426</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6692007</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125400339</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98352</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ramptjärnen, Ramptjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>516442</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6692052</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Niklas Rehn</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>98353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98353</v>
+        <v>98355</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98355</v>
+        <v>98359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -1946,7 +1946,7 @@
         <v>125408915</v>
       </c>
       <c r="B14" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98360</v>
+        <v>98362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98362</v>
+        <v>98364</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98364</v>
+        <v>98366</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -1946,7 +1946,7 @@
         <v>125408915</v>
       </c>
       <c r="B14" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 15914-2024 artfynd.xlsx
+++ b/artfynd/A 15914-2024 artfynd.xlsx
@@ -1946,7 +1946,7 @@
         <v>125408915</v>
       </c>
       <c r="B14" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>125400339</v>
       </c>
       <c r="B15" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
